--- a/02_tuberculosis/data/WHO_TB_2023.xlsx
+++ b/02_tuberculosis/data/WHO_TB_2023.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0074e9bac09c33d7/デスクトップ/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yuichiyazaki/Library/CloudStorage/Dropbox/Projects_External/prj_グローバルファンド/prj_jcie/02_tuberculosis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1529792-EC0F-46AE-9C63-F9D694AF3FBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{088D172E-DECA-764D-8691-F35DAD7B2DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E4A2B538-B1A7-43E4-8F74-E50E269AC717}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="23260" windowHeight="12460" activeTab="1" xr2:uid="{E4A2B538-B1A7-43E4-8F74-E50E269AC717}"/>
   </bookViews>
   <sheets>
-    <sheet name="WHO_TB_2023" sheetId="1" r:id="rId1"/>
+    <sheet name="en" sheetId="1" r:id="rId1"/>
+    <sheet name="ja" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>WHO Africa Region</t>
     <phoneticPr fontId="1"/>
@@ -78,13 +79,46 @@
   <si>
     <t>WHO Global</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>総結核罹患率</t>
+  </si>
+  <si>
+    <t>結核罹患率（10万人あたり）</t>
+  </si>
+  <si>
+    <t>HIV陽性者の結核罹患率</t>
+  </si>
+  <si>
+    <t>HIV陽性者の結核罹患率（10万人あたり）</t>
+  </si>
+  <si>
+    <t>WHOアフリカ地域</t>
+  </si>
+  <si>
+    <t>WHO/PAHOアメリカ大陸地域</t>
+  </si>
+  <si>
+    <t>WHO東地中海地域</t>
+  </si>
+  <si>
+    <t>WHOヨーロッパ地域</t>
+  </si>
+  <si>
+    <t>WHO東南アジア地域</t>
+  </si>
+  <si>
+    <t>WHO西太平洋地域</t>
+  </si>
+  <si>
+    <t>WHO世界</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,9 +179,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -185,7 +219,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -291,7 +325,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -433,7 +467,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -442,16 +476,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4B68950-47AB-444B-AF2E-685B0A7C210F}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="33.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.19921875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="30.09765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38.19921875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.5" customWidth="1"/>
+    <col min="3" max="3" width="20.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="B1" t="s">
         <v>1</v>
       </c>
@@ -465,7 +499,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -482,7 +516,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -499,7 +533,7 @@
         <v>4.0999999999999996</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -516,7 +550,7 @@
         <v>0.57999999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -533,7 +567,7 @@
         <v>3.1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -550,7 +584,7 @@
         <v>4.7</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -567,7 +601,7 @@
         <v>1.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -587,5 +621,158 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AF68309-0C37-3543-B71D-1FF8CFF749CD}">
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="33.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.5" customWidth="1"/>
+    <col min="4" max="4" width="30.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.1640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="B1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2">
+        <v>2550000</v>
+      </c>
+      <c r="C2">
+        <v>206</v>
+      </c>
+      <c r="D2">
+        <v>461000</v>
+      </c>
+      <c r="E2">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3">
+        <v>342000</v>
+      </c>
+      <c r="C3">
+        <v>33</v>
+      </c>
+      <c r="D3">
+        <v>42000</v>
+      </c>
+      <c r="E3">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <v>936000</v>
+      </c>
+      <c r="C4">
+        <v>116</v>
+      </c>
+      <c r="D4">
+        <v>4700</v>
+      </c>
+      <c r="E4">
+        <v>0.57999999999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5">
+        <v>225000</v>
+      </c>
+      <c r="C5">
+        <v>24</v>
+      </c>
+      <c r="D5">
+        <v>29000</v>
+      </c>
+      <c r="E5">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6">
+        <v>4910100</v>
+      </c>
+      <c r="C6">
+        <v>234</v>
+      </c>
+      <c r="D6">
+        <v>99000</v>
+      </c>
+      <c r="E6">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>1880000</v>
+      </c>
+      <c r="C7">
+        <v>97</v>
+      </c>
+      <c r="D7">
+        <v>25000</v>
+      </c>
+      <c r="E7">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>10800000</v>
+      </c>
+      <c r="C8">
+        <v>134</v>
+      </c>
+      <c r="D8">
+        <v>662000</v>
+      </c>
+      <c r="E8">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>